--- a/multi seed generators/merged 10 seeds/regression/results/aggregated/utility_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/regression/results/aggregated/utility_mean_sd.xlsx
@@ -105,7 +105,7 @@
     <col min="13" max="13" width="23" customWidth="1"/>
     <col min="14" max="14" width="23" customWidth="1"/>
     <col min="15" max="15" width="23" customWidth="1"/>
-    <col min="16" max="16" width="23" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
@@ -334,11 +334,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -547,11 +547,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
@@ -760,11 +760,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -973,11 +973,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R12" s="2" t="n">
@@ -1186,11 +1186,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -1399,11 +1399,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R18" s="2" t="n">
@@ -1612,11 +1612,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -1825,11 +1825,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R24" s="2" t="n">
@@ -2038,11 +2038,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -2251,11 +2251,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R30" s="2" t="n">
@@ -2464,11 +2464,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -2677,11 +2677,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R36" s="2" t="n">
@@ -2819,11 +2819,11 @@
         <v>3.2300671118926934</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.0</v>
+        <v>0.41216680506041453</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.23007 ± 0</t>
+          <t xml:space="preserve">3.23007 ± 0.412167</t>
         </is>
       </c>
       <c r="R38" s="2" t="n">
@@ -2890,11 +2890,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -2961,11 +2961,11 @@
         <v>3.605952757328024</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>0.0</v>
+        <v>0.1660113521529581</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.60595 ± 0</t>
+          <t xml:space="preserve">3.60595 ± 0.166011</t>
         </is>
       </c>
       <c r="R40" s="2" t="n">
@@ -3032,11 +3032,11 @@
         <v>0.074916165247085</v>
       </c>
       <c r="P41" t="n">
-        <v>0.0</v>
+        <v>0.059340847416627165</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0749162 ± 0</t>
+          <t xml:space="preserve">0.0749162 ± 0.0593408</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -3103,11 +3103,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R42" s="2" t="n">
@@ -3174,11 +3174,11 @@
         <v>0.9247419656410022</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0</v>
+        <v>0.059339811560804166</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.924742 ± 0</t>
+          <t xml:space="preserve">0.924742 ± 0.0593398</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -3245,11 +3245,11 @@
         <v>9.096777018801081</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.0</v>
+        <v>4.633987147057834</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.09678 ± 0</t>
+          <t xml:space="preserve">9.09678 ± 4.63399</t>
         </is>
       </c>
       <c r="R44" s="2" t="n">
@@ -3316,11 +3316,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -3387,11 +3387,11 @@
         <v>9.609014699568137</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>0.0</v>
+        <v>4.605666584232684</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.60901 ± 0</t>
+          <t xml:space="preserve">9.60901 ± 4.60567</t>
         </is>
       </c>
       <c r="R46" s="2" t="n">
@@ -3529,11 +3529,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R48" s="2" t="n">
@@ -3742,11 +3742,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -3955,11 +3955,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R54" s="2" t="n">
@@ -4168,11 +4168,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -4381,11 +4381,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R60" s="2" t="n">
@@ -4594,11 +4594,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -4807,11 +4807,11 @@
         <v>0.37588564543533</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37725549187527585</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.375886 ± 0</t>
+          <t xml:space="preserve">0.375886 ± 0.377255</t>
         </is>
       </c>
       <c r="R66" s="2" t="n">
@@ -5020,11 +5020,11 @@
         <v>0.999658130888087</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0</v>
+        <v>0.00035062237760726824</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.999658 ± 0</t>
+          <t xml:space="preserve">0.999658 ± 0.000350622</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -5233,11 +5233,11 @@
         <v>0.5122376807670548</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5115390444332104</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.512238 ± 0</t>
+          <t xml:space="preserve">0.512238 ± 0.511539</t>
         </is>
       </c>
       <c r="R72" s="2" t="n">
@@ -5446,11 +5446,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -5659,11 +5659,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R78" s="2" t="n">
@@ -5872,11 +5872,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -6085,11 +6085,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R84" s="2" t="n">
@@ -6298,11 +6298,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -6511,11 +6511,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R90" s="2" t="n">
@@ -6724,11 +6724,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P93" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R93" t="n">
@@ -6937,11 +6937,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R96" s="2" t="n">
@@ -7150,11 +7150,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -7363,11 +7363,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R102" s="2" t="n">
@@ -7576,11 +7576,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -7789,11 +7789,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R108" s="2" t="n">
@@ -7931,11 +7931,11 @@
         <v>6.582174093992501</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>0.0</v>
+        <v>5.9850966597132444</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.58217 ± 0</t>
+          <t xml:space="preserve">6.58217 ± 5.9851</t>
         </is>
       </c>
       <c r="R110" s="2" t="n">
@@ -8002,11 +8002,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P111" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -8073,11 +8073,11 @@
         <v>12.374335475594531</v>
       </c>
       <c r="P112" s="2" t="n">
-        <v>0.0</v>
+        <v>5.639433719545623</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.3743 ± 0</t>
+          <t xml:space="preserve">12.3743 ± 5.63943</t>
         </is>
       </c>
       <c r="R112" s="2" t="n">
@@ -8144,11 +8144,11 @@
         <v>0.9027790240778379</v>
       </c>
       <c r="P113" t="n">
-        <v>0.0</v>
+        <v>0.8715377486572258</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902779 ± 0</t>
+          <t xml:space="preserve">0.902779 ± 0.871538</t>
         </is>
       </c>
       <c r="R113" t="n">
@@ -8215,11 +8215,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R114" s="2" t="n">
@@ -8286,11 +8286,11 @@
         <v>-0.1496611213009582</v>
       </c>
       <c r="P115" t="n">
-        <v>0.0</v>
+        <v>0.8619610077873422</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.149661 ± 0</t>
+          <t xml:space="preserve">-0.149661 ± 0.861961</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -8357,11 +8357,11 @@
         <v>8.093266346757641</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>0.0</v>
+        <v>7.358592654626764</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.09327 ± 0</t>
+          <t xml:space="preserve">8.09327 ± 7.35859</t>
         </is>
       </c>
       <c r="R116" s="2" t="n">
@@ -8428,11 +8428,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P117" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -8499,11 +8499,11 @@
         <v>15.7868418118509</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>0.0</v>
+        <v>7.035005174473795</v>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.7868 ± 0</t>
+          <t xml:space="preserve">15.7868 ± 7.03501</t>
         </is>
       </c>
       <c r="R118" s="2" t="n">
@@ -8641,11 +8641,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R120" s="2" t="n">
@@ -8854,11 +8854,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P123" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -9067,11 +9067,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R126" s="2" t="n">
@@ -9280,11 +9280,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P129" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R129" t="n">
@@ -9493,11 +9493,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -9706,11 +9706,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P135" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -9919,11 +9919,11 @@
         <v>5.792161381602034</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0045371907157175</v>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.79216 ± 0</t>
+          <t xml:space="preserve">5.79216 ± 2.00454</t>
         </is>
       </c>
       <c r="R138" s="2" t="n">
@@ -10132,11 +10132,11 @@
         <v>0.7531179027768801</v>
       </c>
       <c r="P141" t="n">
-        <v>0.0</v>
+        <v>0.12884590947614577</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753118 ± 0</t>
+          <t xml:space="preserve">0.753118 ± 0.128846</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -10345,11 +10345,11 @@
         <v>7.693575465093256</v>
       </c>
       <c r="P144" s="2" t="n">
-        <v>0.0</v>
+        <v>2.1581445854839942</v>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.69358 ± 0</t>
+          <t xml:space="preserve">7.69358 ± 2.15814</t>
         </is>
       </c>
       <c r="R144" s="2" t="n">
@@ -10558,11 +10558,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P147" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R147" t="n">
@@ -10771,11 +10771,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P150" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R150" s="2" t="n">
@@ -10984,11 +10984,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P153" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R153" t="n">
@@ -11197,11 +11197,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P156" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R156" s="2" t="n">
@@ -11410,11 +11410,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P159" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R159" t="n">
@@ -11623,11 +11623,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R162" s="2" t="n">
@@ -11836,11 +11836,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P165" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R165" t="n">
@@ -12049,11 +12049,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P168" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R168" s="2" t="n">
@@ -12262,11 +12262,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P171" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R171" t="n">
@@ -12475,11 +12475,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P174" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R174" s="2" t="n">
@@ -12688,11 +12688,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P177" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R177" t="n">
@@ -12901,11 +12901,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P180" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R180" s="2" t="n">
@@ -13043,11 +13043,11 @@
         <v>2.01019545726001</v>
       </c>
       <c r="P182" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4901707467643681</v>
       </c>
       <c r="Q182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0102 ± 0</t>
+          <t xml:space="preserve">2.0102 ± 0.490171</t>
         </is>
       </c>
       <c r="R182" s="2" t="n">
@@ -13114,11 +13114,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P183" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R183" t="n">
@@ -13185,11 +13185,11 @@
         <v>2.913878983413816</v>
       </c>
       <c r="P184" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04285118720798725</v>
       </c>
       <c r="Q184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.91388 ± 0</t>
+          <t xml:space="preserve">2.91388 ± 0.0428512</t>
         </is>
       </c>
       <c r="R184" s="2" t="n">
@@ -13256,11 +13256,11 @@
         <v>0.08720070413467229</v>
       </c>
       <c r="P185" t="n">
-        <v>0.0</v>
+        <v>0.014971817370764312</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0872007 ± 0</t>
+          <t xml:space="preserve">0.0872007 ± 0.0149718</t>
         </is>
       </c>
       <c r="R185" t="n">
@@ -13327,11 +13327,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P186" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R186" s="2" t="n">
@@ -13398,11 +13398,11 @@
         <v>0.8909013657394501</v>
       </c>
       <c r="P187" t="n">
-        <v>0.0</v>
+        <v>0.002501874074279764</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.890901 ± 0</t>
+          <t xml:space="preserve">0.890901 ± 0.00250187</t>
         </is>
       </c>
       <c r="R187" t="n">
@@ -13469,11 +13469,11 @@
         <v>1.9572510092857862</v>
       </c>
       <c r="P188" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5452965564360638</v>
       </c>
       <c r="Q188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.95725 ± 0</t>
+          <t xml:space="preserve">1.95725 ± 0.545297</t>
         </is>
       </c>
       <c r="R188" s="2" t="n">
@@ -13540,11 +13540,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P189" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R189" t="n">
@@ -13611,11 +13611,11 @@
         <v>3.371957726067914</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03867297152030222</v>
       </c>
       <c r="Q190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.37196 ± 0</t>
+          <t xml:space="preserve">3.37196 ± 0.038673</t>
         </is>
       </c>
       <c r="R190" s="2" t="n">
@@ -13753,11 +13753,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R192" s="2" t="n">
@@ -13966,11 +13966,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P195" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R195" t="n">
@@ -14179,11 +14179,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P198" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R198" s="2" t="n">
@@ -14392,11 +14392,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P201" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R201" t="n">
@@ -14605,11 +14605,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P204" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R204" s="2" t="n">
@@ -14818,11 +14818,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P207" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R207" t="n">
@@ -15031,11 +15031,11 @@
         <v>0.9036835261538059</v>
       </c>
       <c r="P210" s="2" t="n">
-        <v>0.0</v>
+        <v>0.4882941088508076</v>
       </c>
       <c r="Q210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.903684 ± 0</t>
+          <t xml:space="preserve">0.903684 ± 0.488294</t>
         </is>
       </c>
       <c r="R210" s="2" t="n">
@@ -15244,11 +15244,11 @@
         <v>0.9781020698741223</v>
       </c>
       <c r="P213" t="n">
-        <v>0.0</v>
+        <v>0.01476129877415828</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.978102 ± 0</t>
+          <t xml:space="preserve">0.978102 ± 0.0147613</t>
         </is>
       </c>
       <c r="R213" t="n">
@@ -15457,11 +15457,11 @@
         <v>1.414706716782129</v>
       </c>
       <c r="P216" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5439234649606681</v>
       </c>
       <c r="Q216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.41471 ± 0</t>
+          <t xml:space="preserve">1.41471 ± 0.543923</t>
         </is>
       </c>
       <c r="R216" s="2" t="n">
@@ -15670,11 +15670,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P219" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R219" t="n">
@@ -15883,11 +15883,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P222" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R222" s="2" t="n">
@@ -16096,11 +16096,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P225" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R225" t="n">
@@ -16309,11 +16309,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P228" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R228" s="2" t="n">
@@ -16522,11 +16522,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P231" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R231" t="n">
@@ -16735,11 +16735,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P234" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R234" s="2" t="n">
@@ -16948,11 +16948,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P237" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R237" t="n">
@@ -17161,11 +17161,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P240" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R240" s="2" t="n">
@@ -17374,11 +17374,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P243" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R243" t="n">
@@ -17587,11 +17587,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P246" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R246" s="2" t="n">
@@ -17800,11 +17800,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P249" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R249" t="n">
@@ -18013,11 +18013,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P252" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R252" s="2" t="n">
@@ -18155,11 +18155,11 @@
         <v>15.363917670651059</v>
       </c>
       <c r="P254" s="2" t="n">
-        <v>0.0</v>
+        <v>29.22711247291791</v>
       </c>
       <c r="Q254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.3639 ± 0</t>
+          <t xml:space="preserve">15.3639 ± 29.2271</t>
         </is>
       </c>
       <c r="R254" s="2" t="n">
@@ -18226,11 +18226,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P255" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R255" t="n">
@@ -18297,11 +18297,11 @@
         <v>1754.3857978552849</v>
       </c>
       <c r="P256" s="2" t="n">
-        <v>0.0</v>
+        <v>22.117752324650127</v>
       </c>
       <c r="Q256" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1754.39 ± 0</t>
+          <t xml:space="preserve">1754.39 ± 22.1178</t>
         </is>
       </c>
       <c r="R256" s="2" t="n">
@@ -18368,11 +18368,11 @@
         <v>0.01610295765320083</v>
       </c>
       <c r="P257" t="n">
-        <v>0.0</v>
+        <v>0.08981812831875627</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.016103 ± 0</t>
+          <t xml:space="preserve">0.016103 ± 0.0898181</t>
         </is>
       </c>
       <c r="R257" t="n">
@@ -18439,11 +18439,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P258" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R258" s="2" t="n">
@@ -18510,11 +18510,11 @@
         <v>-0.08374332837863</v>
       </c>
       <c r="P259" t="n">
-        <v>0.0</v>
+        <v>0.04030506250168554</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0837433 ± 0</t>
+          <t xml:space="preserve">-0.0837433 ± 0.0403051</t>
         </is>
       </c>
       <c r="R259" t="n">
@@ -18581,11 +18581,11 @@
         <v>16.491714798673</v>
       </c>
       <c r="P260" s="2" t="n">
-        <v>0.0</v>
+        <v>86.36470582233898</v>
       </c>
       <c r="Q260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16.4917 ± 0</t>
+          <t xml:space="preserve">16.4917 ± 86.3647</t>
         </is>
       </c>
       <c r="R260" s="2" t="n">
@@ -18652,11 +18652,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P261" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R261" t="n">
@@ -18723,11 +18723,11 @@
         <v>2071.357530391925</v>
       </c>
       <c r="P262" s="2" t="n">
-        <v>0.0</v>
+        <v>38.454614264568704</v>
       </c>
       <c r="Q262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071.36 ± 0</t>
+          <t xml:space="preserve">2071.36 ± 38.4546</t>
         </is>
       </c>
       <c r="R262" s="2" t="n">
@@ -18865,11 +18865,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P264" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R264" s="2" t="n">
@@ -19078,11 +19078,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P267" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R267" t="n">
@@ -19291,11 +19291,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P270" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R270" s="2" t="n">
@@ -19504,11 +19504,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P273" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R273" t="n">
@@ -19717,11 +19717,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P276" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R276" s="2" t="n">
@@ -19930,11 +19930,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P279" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R279" t="n">
@@ -20143,11 +20143,11 @@
         <v>1739.0218801846343</v>
       </c>
       <c r="P282" s="2" t="n">
-        <v>0.0</v>
+        <v>19.105735673091143</v>
       </c>
       <c r="Q282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739.02 ± 0</t>
+          <t xml:space="preserve">1739.02 ± 19.1057</t>
         </is>
       </c>
       <c r="R282" s="2" t="n">
@@ -20356,11 +20356,11 @@
         <v>-0.06764037072542917</v>
       </c>
       <c r="P285" t="n">
-        <v>0.0</v>
+        <v>0.0802670424982744</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-0.0676404 ± 0</t>
+          <t xml:space="preserve">-0.0676404 ± 0.080267</t>
         </is>
       </c>
       <c r="R285" t="n">
@@ -20569,11 +20569,11 @@
         <v>2054.8658155932526</v>
       </c>
       <c r="P288" s="2" t="n">
-        <v>0.0</v>
+        <v>77.33113896447136</v>
       </c>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054.87 ± 0</t>
+          <t xml:space="preserve">2054.87 ± 77.3311</t>
         </is>
       </c>
       <c r="R288" s="2" t="n">
@@ -20782,11 +20782,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P291" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R291" t="n">
@@ -20995,11 +20995,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P294" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R294" s="2" t="n">
@@ -21208,11 +21208,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P297" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R297" t="n">
@@ -21421,11 +21421,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P300" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R300" s="2" t="n">
@@ -21634,11 +21634,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P303" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R303" t="n">
@@ -21847,11 +21847,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P306" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q306" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R306" s="2" t="n">
@@ -22060,11 +22060,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P309" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R309" t="n">
@@ -22273,11 +22273,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P312" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R312" s="2" t="n">
@@ -22486,11 +22486,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P315" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R315" t="n">
@@ -22699,11 +22699,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P318" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q318" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R318" s="2" t="n">
@@ -22912,11 +22912,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P321" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R321" t="n">
@@ -23125,11 +23125,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P324" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R324" s="2" t="n">
@@ -23267,11 +23267,11 @@
         <v>4.04746190020483</v>
       </c>
       <c r="P326" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2931948822784347</v>
       </c>
       <c r="Q326" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.04746 ± 0</t>
+          <t xml:space="preserve">4.04746 ± 1.29319</t>
         </is>
       </c>
       <c r="R326" s="2" t="n">
@@ -23338,11 +23338,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P327" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R327" t="n">
@@ -23409,11 +23409,11 @@
         <v>7.23017434437224</v>
       </c>
       <c r="P328" s="2" t="n">
-        <v>0.0</v>
+        <v>0.37613110913321485</v>
       </c>
       <c r="Q328" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.23017 ± 0</t>
+          <t xml:space="preserve">7.23017 ± 0.376131</t>
         </is>
       </c>
       <c r="R328" s="2" t="n">
@@ -23480,11 +23480,11 @@
         <v>0.3547480059005065</v>
       </c>
       <c r="P329" t="n">
-        <v>0.0</v>
+        <v>0.05373184814046198</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.354748 ± 0</t>
+          <t xml:space="preserve">0.354748 ± 0.0537318</t>
         </is>
       </c>
       <c r="R329" t="n">
@@ -23551,11 +23551,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P330" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q330" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R330" s="2" t="n">
@@ -23622,11 +23622,11 @@
         <v>0.4827027521449584</v>
       </c>
       <c r="P331" t="n">
-        <v>0.0</v>
+        <v>0.039289460494206535</v>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.482703 ± 0</t>
+          <t xml:space="preserve">0.482703 ± 0.0392895</t>
         </is>
       </c>
       <c r="R331" t="n">
@@ -23693,11 +23693,11 @@
         <v>4.1752040520332</v>
       </c>
       <c r="P332" s="2" t="n">
-        <v>0.0</v>
+        <v>0.699174252212212</v>
       </c>
       <c r="Q332" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1752 ± 0</t>
+          <t xml:space="preserve">4.1752 ± 0.699174</t>
         </is>
       </c>
       <c r="R332" s="2" t="n">
@@ -23764,11 +23764,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P333" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R333" t="n">
@@ -23835,11 +23835,11 @@
         <v>9.435571216406363</v>
       </c>
       <c r="P334" s="2" t="n">
-        <v>0.0</v>
+        <v>0.35815272968587747</v>
       </c>
       <c r="Q334" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.43557 ± 0</t>
+          <t xml:space="preserve">9.43557 ± 0.358153</t>
         </is>
       </c>
       <c r="R334" s="2" t="n">
@@ -23977,11 +23977,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P336" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q336" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R336" s="2" t="n">
@@ -24190,11 +24190,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P339" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R339" t="n">
@@ -24403,11 +24403,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P342" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R342" s="2" t="n">
@@ -24616,11 +24616,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P345" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R345" t="n">
@@ -24829,11 +24829,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P348" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q348" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R348" s="2" t="n">
@@ -25042,11 +25042,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P351" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R351" t="n">
@@ -25255,11 +25255,11 @@
         <v>3.18271244416741</v>
       </c>
       <c r="P354" s="2" t="n">
-        <v>0.0</v>
+        <v>1.2372867057773442</v>
       </c>
       <c r="Q354" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.18271 ± 0</t>
+          <t xml:space="preserve">3.18271 ± 1.23729</t>
         </is>
       </c>
       <c r="R354" s="2" t="n">
@@ -25468,11 +25468,11 @@
         <v>0.8374507580454648</v>
       </c>
       <c r="P357" t="n">
-        <v>0.0</v>
+        <v>0.03665310080557785</v>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.837451 ± 0</t>
+          <t xml:space="preserve">0.837451 ± 0.0366531</t>
         </is>
       </c>
       <c r="R357" t="n">
@@ -25681,11 +25681,11 @@
         <v>5.260367164373164</v>
       </c>
       <c r="P360" s="2" t="n">
-        <v>0.0</v>
+        <v>0.600475858944438</v>
       </c>
       <c r="Q360" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.26037 ± 0</t>
+          <t xml:space="preserve">5.26037 ± 0.600476</t>
         </is>
       </c>
       <c r="R360" s="2" t="n">
@@ -25894,11 +25894,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P363" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R363" t="n">
@@ -26107,11 +26107,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P366" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q366" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R366" s="2" t="n">
@@ -26320,11 +26320,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P369" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R369" t="n">
@@ -26533,11 +26533,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P372" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q372" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R372" s="2" t="n">
@@ -26746,11 +26746,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P375" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R375" t="n">
@@ -26959,11 +26959,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P378" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q378" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R378" s="2" t="n">
@@ -27172,11 +27172,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P381" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R381" t="n">
@@ -27385,11 +27385,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P384" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q384" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R384" s="2" t="n">
@@ -27598,11 +27598,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P387" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R387" t="n">
@@ -27811,11 +27811,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P390" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q390" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R390" s="2" t="n">
@@ -28024,11 +28024,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P393" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R393" t="n">
@@ -28237,11 +28237,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P396" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q396" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R396" s="2" t="n">
@@ -28379,11 +28379,11 @@
         <v>1.553241212660327</v>
       </c>
       <c r="P398" s="2" t="n">
-        <v>0.0</v>
+        <v>0.8049664160708678</v>
       </c>
       <c r="Q398" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.55324 ± 0</t>
+          <t xml:space="preserve">1.55324 ± 0.804966</t>
         </is>
       </c>
       <c r="R398" s="2" t="n">
@@ -28450,11 +28450,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P399" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R399" t="n">
@@ -28521,11 +28521,11 @@
         <v>6.32536924193509</v>
       </c>
       <c r="P400" s="2" t="n">
-        <v>0.0</v>
+        <v>0.5404484788989303</v>
       </c>
       <c r="Q400" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.32537 ± 0</t>
+          <t xml:space="preserve">6.32537 ± 0.540448</t>
         </is>
       </c>
       <c r="R400" s="2" t="n">
@@ -28592,11 +28592,11 @@
         <v>0.20431523386331302</v>
       </c>
       <c r="P401" t="n">
-        <v>0.0</v>
+        <v>0.06230496116149596</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.204315 ± 0</t>
+          <t xml:space="preserve">0.204315 ± 0.062305</t>
         </is>
       </c>
       <c r="R401" t="n">
@@ -28663,11 +28663,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P402" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q402" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R402" s="2" t="n">
@@ -28734,11 +28734,11 @@
         <v>0.5302727668614803</v>
       </c>
       <c r="P403" t="n">
-        <v>0.0</v>
+        <v>0.00862516832005052</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.530273 ± 0</t>
+          <t xml:space="preserve">0.530273 ± 0.00862517</t>
         </is>
       </c>
       <c r="R403" t="n">
@@ -28805,11 +28805,11 @@
         <v>2.2475780087928205</v>
       </c>
       <c r="P404" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7860253641842126</v>
       </c>
       <c r="Q404" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.24758 ± 0</t>
+          <t xml:space="preserve">2.24758 ± 0.786025</t>
         </is>
       </c>
       <c r="R404" s="2" t="n">
@@ -28876,11 +28876,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P405" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R405" t="n">
@@ -28947,11 +28947,11 @@
         <v>8.876660159144524</v>
       </c>
       <c r="P406" s="2" t="n">
-        <v>0.0</v>
+        <v>0.08094861643816746</v>
       </c>
       <c r="Q406" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.87666 ± 0</t>
+          <t xml:space="preserve">8.87666 ± 0.0809486</t>
         </is>
       </c>
       <c r="R406" s="2" t="n">
@@ -29089,11 +29089,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P408" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q408" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R408" s="2" t="n">
@@ -29302,11 +29302,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P411" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q411" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R411" t="n">
@@ -29515,11 +29515,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P414" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q414" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R414" s="2" t="n">
@@ -29728,11 +29728,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P417" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R417" t="n">
@@ -29941,11 +29941,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P420" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q420" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R420" s="2" t="n">
@@ -30154,11 +30154,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P423" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R423" t="n">
@@ -30367,11 +30367,11 @@
         <v>4.7721280292747625</v>
       </c>
       <c r="P426" s="2" t="n">
-        <v>0.0</v>
+        <v>0.596562128078719</v>
       </c>
       <c r="Q426" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77213 ± 0</t>
+          <t xml:space="preserve">4.77213 ± 0.596562</t>
         </is>
       </c>
       <c r="R426" s="2" t="n">
@@ -30580,11 +30580,11 @@
         <v>0.7345880007247932</v>
       </c>
       <c r="P429" t="n">
-        <v>0.0</v>
+        <v>0.06170506184087588</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.734588 ± 0</t>
+          <t xml:space="preserve">0.734588 ± 0.0617051</t>
         </is>
       </c>
       <c r="R429" t="n">
@@ -30793,11 +30793,11 @@
         <v>6.629082150351707</v>
       </c>
       <c r="P432" s="2" t="n">
-        <v>0.0</v>
+        <v>0.7818460172167346</v>
       </c>
       <c r="Q432" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.62908 ± 0</t>
+          <t xml:space="preserve">6.62908 ± 0.781846</t>
         </is>
       </c>
       <c r="R432" s="2" t="n">
